--- a/data/trans_dic/P39A5_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,4; 91,9</t>
+          <t>86,21; 92,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,44; 91,43</t>
+          <t>86,39; 91,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,04; 91,05</t>
+          <t>87,22; 91,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,78; 92,73</t>
+          <t>86,88; 92,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,03; 88,65</t>
+          <t>82,34; 88,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,71; 90,09</t>
+          <t>85,96; 90,24</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,41; 97,15</t>
+          <t>85,6; 96,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,12; 88,51</t>
+          <t>80,14; 88,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,07; 95,77</t>
+          <t>85,38; 96,73</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,49; 88,1</t>
+          <t>83,35; 88,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,79; 94,1</t>
+          <t>83,8; 93,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,81; 91,02</t>
+          <t>84,68; 91,11</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,49; 87,98</t>
+          <t>80,09; 88,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,96; 84,65</t>
+          <t>54,5; 84,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,42; 84,75</t>
+          <t>61,33; 84,82</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,82; 91,9</t>
+          <t>75,5; 92,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86,86; 91,28</t>
+          <t>86,62; 91,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,59</t>
+          <t>85,41; 90,64</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,26; 90,83</t>
+          <t>86,31; 90,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,82; 87,97</t>
+          <t>77,65; 87,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83,61; 88,44</t>
+          <t>83,79; 88,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>419369; 446027</t>
+          <t>418447; 447144</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>374552; 396170</t>
+          <t>374332; 395976</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>799655; 836419</t>
+          <t>801292; 837485</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>378653; 404617</t>
+          <t>379100; 403597</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>297305; 321282</t>
+          <t>298414; 321253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>684664; 719624</t>
+          <t>686652; 720796</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>550215; 625854</t>
+          <t>551417; 623894</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123605; 138276</t>
+          <t>125208; 138726</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>680941; 766546</t>
+          <t>683376; 774280</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>799201; 843331</t>
+          <t>797841; 842641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>787735; 884632</t>
+          <t>787837; 876696</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1609199; 1727069</t>
+          <t>1606702; 1728681</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>321776; 356118</t>
+          <t>324198; 357130</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>363760; 604223</t>
+          <t>389038; 605954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>664699; 948038</t>
+          <t>686093; 948844</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>152933; 187858</t>
+          <t>154327; 189816</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>576878; 606206</t>
+          <t>575305; 604646</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>743541; 786797</t>
+          <t>741876; 787273</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2701945; 2845039</t>
+          <t>2703421; 2841384</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2577475; 2876671</t>
+          <t>2539122; 2870774</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5353126; 5662380</t>
+          <t>5364531; 5668928</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A5_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,21; 92,13</t>
+          <t>86,36; 92,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,39; 91,38</t>
+          <t>85,68; 90,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,22; 91,16</t>
+          <t>87,19; 90,83</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,88; 92,5</t>
+          <t>87,48; 92,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,34; 88,64</t>
+          <t>82,61; 88,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,96; 90,24</t>
+          <t>86,13; 90,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,6; 96,85</t>
+          <t>82,57; 89,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,14; 88,79</t>
+          <t>79,54; 88,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,38; 96,73</t>
+          <t>83,16; 88,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,35; 88,03</t>
+          <t>82,79; 87,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,8; 93,25</t>
+          <t>81,98; 86,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,68; 91,11</t>
+          <t>83,3; 86,55</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,09; 88,23</t>
+          <t>78,81; 86,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,5; 84,89</t>
+          <t>81,33; 85,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,33; 84,82</t>
+          <t>81,32; 85,64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,5; 92,86</t>
+          <t>79,57; 93,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86,62; 91,04</t>
+          <t>86,38; 90,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,41; 90,64</t>
+          <t>86,1; 90,67</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,31; 90,71</t>
+          <t>85,31; 87,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,65; 87,79</t>
+          <t>84,94; 87,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83,79; 88,54</t>
+          <t>85,48; 87,12</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>434608</t>
+          <t>472468</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>385917</t>
+          <t>418432</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>820524</t>
+          <t>890899</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>418447; 447144</t>
+          <t>456072; 486168</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>374332; 395976</t>
+          <t>404775; 429272</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>801292; 837485</t>
+          <t>872333; 908768</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>393184</t>
+          <t>419869</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>310889</t>
+          <t>343486</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>704073</t>
+          <t>763355</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>379100; 403597</t>
+          <t>406070; 431123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>298414; 321253</t>
+          <t>329859; 354574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>686652; 720796</t>
+          <t>743647; 779401</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>590929</t>
+          <t>380895</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>132192</t>
+          <t>148204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>723121</t>
+          <t>529100</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>551417; 623894</t>
+          <t>363586; 394942</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>125208; 138726</t>
+          <t>139575; 155480</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>683376; 774280</t>
+          <t>512137; 545085</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>822327</t>
+          <t>887740</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>827542</t>
+          <t>689596</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1649869</t>
+          <t>1577336</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>797841; 842641</t>
+          <t>863952; 911025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>787837; 876696</t>
+          <t>669837; 707584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1606702; 1728681</t>
+          <t>1549818; 1610416</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>342061</t>
+          <t>387267</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>541140</t>
+          <t>601167</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>883201</t>
+          <t>988434</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>324198; 357130</t>
+          <t>367508; 403012</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>389038; 605954</t>
+          <t>584939; 616391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>686093; 948844</t>
+          <t>964148; 1015336</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>175909</t>
+          <t>175190</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>592012</t>
+          <t>655453</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>767921</t>
+          <t>830643</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>154327; 189816</t>
+          <t>158484; 186726</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>575305; 604646</t>
+          <t>637861; 671882</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>741876; 787273</t>
+          <t>807246; 850109</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2759018</t>
+          <t>2723428</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2789691</t>
+          <t>2856339</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5548710</t>
+          <t>5579766</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2703421; 2841384</t>
+          <t>2680014; 2762949</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2539122; 2870774</t>
+          <t>2821553; 2893033</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5364531; 5668928</t>
+          <t>5524902; 5631247</t>
         </is>
       </c>
     </row>
